--- a/outputs/design_sweep/design_study/nominal_candidate_1_verified/params.xlsx
+++ b/outputs/design_sweep/design_study/nominal_candidate_1_verified/params.xlsx
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3600</v>
+        <v>3374.214216762803</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1800</v>
+        <v>1687.107108381402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>323.4825</v>
+        <v>334.0034173953844</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>390</v>
+        <v>400.5209173953844</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.50000000000001</v>
+        <v>22.75000000000001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.62500000000001</v>
+        <v>17.06250000000001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>898.1994793308148</v>
+        <v>868.8316411787061</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>449.0997396654074</v>
+        <v>434.4158205893531</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1003.194117647059</v>
+        <v>994.6305988316049</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1050</v>
+        <v>1041.436481184546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>551.1383292383292</v>
+        <v>300</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1019.783333333334</v>
+        <v>991.8608912081182</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1050</v>
+        <v>1022.077557874785</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9.750000000000005</v>
+        <v>7.250000000000003</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7.312500000000004</v>
+        <v>5.437500000000003</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>130.6</v>
+        <v>144.2267672041623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>709.4</v>
+        <v>723.0267672041624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>337.336</v>
+        <v>380</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>159.069</v>
+        <v>150.8290738714257</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>519.2860000000001</v>
+        <v>538.048711295145</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
